--- a/AtchisonRegime/Outputs/India/MSCI_Europe/df_regSettingsMSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/India/MSCI_Europe/df_regSettingsMSCI_Europe.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I316"/>
+  <dimension ref="A1:I317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10521,7 +10521,7 @@
         <v>-1.609197597460336</v>
       </c>
       <c r="C306" t="n">
-        <v>0.1269752971138792</v>
+        <v>-0.1586595595287259</v>
       </c>
       <c r="D306" t="b">
         <v>0</v>
@@ -10554,7 +10554,7 @@
         <v>-1.665486013574585</v>
       </c>
       <c r="C307" t="n">
-        <v>0.08629259774089702</v>
+        <v>0.1383565447898576</v>
       </c>
       <c r="D307" t="b">
         <v>0</v>
@@ -10587,7 +10587,7 @@
         <v>-1.901181816225073</v>
       </c>
       <c r="C308" t="n">
-        <v>0.06631902283450167</v>
+        <v>0.1152177262296182</v>
       </c>
       <c r="D308" t="b">
         <v>0</v>
@@ -10620,7 +10620,7 @@
         <v>-2.093900900681109</v>
       </c>
       <c r="C309" t="n">
-        <v>0.04555869256656515</v>
+        <v>0.09314547075106079</v>
       </c>
       <c r="D309" t="b">
         <v>0</v>
@@ -10653,7 +10653,7 @@
         <v>-1.925045594804248</v>
       </c>
       <c r="C310" t="n">
-        <v>0</v>
+        <v>0.0730366768494552</v>
       </c>
       <c r="D310" t="b">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>-1.272591127701468</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.04929692066057501</v>
+        <v>0.05992091312749612</v>
       </c>
       <c r="D311" t="b">
         <v>0</v>
@@ -10719,13 +10719,13 @@
         <v>-0.8244531695587767</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.05176467051398125</v>
+        <v>0.05405871173099788</v>
       </c>
       <c r="D312" t="b">
         <v>0</v>
       </c>
       <c r="E312" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F312" t="n">
         <v>-1.1038301565745</v>
@@ -10735,12 +10735,12 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Type 3</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -10752,13 +10752,13 @@
         <v>-0.9488965089988395</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.08209071111419658</v>
+        <v>0.05316714534512307</v>
       </c>
       <c r="D313" t="b">
         <v>0</v>
       </c>
       <c r="E313" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F313" t="n">
         <v>2.70141072687946</v>
@@ -10768,12 +10768,12 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>Type 3</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -10785,13 +10785,13 @@
         <v>-1.209590239554617</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.05812943059160887</v>
+        <v>0.06021053671922057</v>
       </c>
       <c r="D314" t="b">
         <v>0</v>
       </c>
       <c r="E314" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F314" t="n">
         <v>6.12278993736941</v>
@@ -10801,12 +10801,12 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>Type 3</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -10818,13 +10818,13 @@
         <v>-1.426764933004604</v>
       </c>
       <c r="C315" t="n">
-        <v>-0.09280608837336365</v>
+        <v>0.07188992918729449</v>
       </c>
       <c r="D315" t="b">
         <v>0</v>
       </c>
       <c r="E315" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F315" t="n">
         <v>3.97735373678266</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Type 3</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -10848,16 +10848,16 @@
         <v>45747</v>
       </c>
       <c r="B316" t="n">
-        <v>-1.542312882396952</v>
+        <v>-1.479076778638796</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.1977619446671215</v>
+        <v>0.08487070723497196</v>
       </c>
       <c r="D316" t="b">
         <v>0</v>
       </c>
       <c r="E316" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F316" t="n">
         <v>1.83191753619591</v>
@@ -10867,12 +10867,45 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Type 3</t>
+          <t>Type 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B317" t="n">
+        <v>-1.432151479563748</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.09460631327380538</v>
+      </c>
+      <c r="D317" t="b">
+        <v>0</v>
+      </c>
+      <c r="E317" t="b">
+        <v>1</v>
+      </c>
+      <c r="F317" t="n">
+        <v>1.83191753619591</v>
+      </c>
+      <c r="G317" t="n">
+        <v>325618.0893537902</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
